--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/46.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/46.xlsx
@@ -426,13 +426,13 @@
         <v>-18.41896912386022</v>
       </c>
       <c r="E2">
-        <v>-35.08320195449875</v>
+        <v>-29.4636419478943</v>
       </c>
       <c r="F2">
-        <v>-4.856369487184431</v>
+        <v>-2.468463767993394</v>
       </c>
       <c r="G2">
-        <v>-22.71523157055741</v>
+        <v>-20.64226064914089</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.17658915581913</v>
       </c>
       <c r="E3">
-        <v>-35.63563729140547</v>
+        <v>-29.0795345183267</v>
       </c>
       <c r="F3">
-        <v>-5.431164515945577</v>
+        <v>-2.394023359708219</v>
       </c>
       <c r="G3">
-        <v>-22.03342968256282</v>
+        <v>-20.57739878566272</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.89775983503059</v>
       </c>
       <c r="E4">
-        <v>-35.58410099296117</v>
+        <v>-29.93631274362991</v>
       </c>
       <c r="F4">
-        <v>-4.783753143920221</v>
+        <v>-2.120364732886777</v>
       </c>
       <c r="G4">
-        <v>-21.83832268120587</v>
+        <v>-19.6654858430517</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.58923437461048</v>
       </c>
       <c r="E5">
-        <v>-35.81919219259537</v>
+        <v>-30.77007726402615</v>
       </c>
       <c r="F5">
-        <v>-4.783008441625103</v>
+        <v>-2.383629833905294</v>
       </c>
       <c r="G5">
-        <v>-21.3379519309455</v>
+        <v>-19.01773457120128</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.27080463975776</v>
       </c>
       <c r="E6">
-        <v>-35.65091409847034</v>
+        <v>-30.70037952057409</v>
       </c>
       <c r="F6">
-        <v>-4.974338945751914</v>
+        <v>-2.413583599190524</v>
       </c>
       <c r="G6">
-        <v>-21.08309785896855</v>
+        <v>-19.19373972479663</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.95753385922369</v>
       </c>
       <c r="E7">
-        <v>-36.27883909708492</v>
+        <v>-30.73871305304902</v>
       </c>
       <c r="F7">
-        <v>-4.644683510868628</v>
+        <v>-2.25149860621955</v>
       </c>
       <c r="G7">
-        <v>-21.02466673020042</v>
+        <v>-18.766834945871</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.6520392235422</v>
       </c>
       <c r="E8">
-        <v>-36.10872017827577</v>
+        <v>-31.8801511544744</v>
       </c>
       <c r="F8">
-        <v>-5.453899059315409</v>
+        <v>-2.209256010513789</v>
       </c>
       <c r="G8">
-        <v>-21.0491333170084</v>
+        <v>-18.6134606815821</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.35462194266758</v>
       </c>
       <c r="E9">
-        <v>-38.29380398493088</v>
+        <v>-32.52703008104808</v>
       </c>
       <c r="F9">
-        <v>-5.097809592241388</v>
+        <v>-2.201959750429931</v>
       </c>
       <c r="G9">
-        <v>-21.26470776616189</v>
+        <v>-18.26062273800658</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.09808032160566</v>
       </c>
       <c r="E10">
-        <v>-38.50864611303978</v>
+        <v>-33.14444222725386</v>
       </c>
       <c r="F10">
-        <v>-4.954417538081988</v>
+        <v>-2.086848987769509</v>
       </c>
       <c r="G10">
-        <v>-20.35026556675886</v>
+        <v>-17.73526233474302</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.90084012623776</v>
       </c>
       <c r="E11">
-        <v>-37.65319925909482</v>
+        <v>-33.17523811474302</v>
       </c>
       <c r="F11">
-        <v>-5.004214016133878</v>
+        <v>-2.053957003306549</v>
       </c>
       <c r="G11">
-        <v>-20.08196240352863</v>
+        <v>-16.96412372009842</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.76961149371578</v>
       </c>
       <c r="E12">
-        <v>-38.17686746486781</v>
+        <v>-33.77392275669008</v>
       </c>
       <c r="F12">
-        <v>-5.133549503835173</v>
+        <v>-2.107979811847521</v>
       </c>
       <c r="G12">
-        <v>-19.60649026626912</v>
+        <v>-16.4111169510364</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.70663504550894</v>
       </c>
       <c r="E13">
-        <v>-39.17091732276554</v>
+        <v>-34.10687427963003</v>
       </c>
       <c r="F13">
-        <v>-4.701980855752868</v>
+        <v>-2.044217887751835</v>
       </c>
       <c r="G13">
-        <v>-19.120682605836</v>
+        <v>-16.37885899530175</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.74086831670281</v>
       </c>
       <c r="E14">
-        <v>-40.26990098036901</v>
+        <v>-35.18099661493139</v>
       </c>
       <c r="F14">
-        <v>-4.849265408338022</v>
+        <v>-1.875743697003069</v>
       </c>
       <c r="G14">
-        <v>-19.58881526363495</v>
+        <v>-16.19183469087893</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.87393070090346</v>
       </c>
       <c r="E15">
-        <v>-39.86569844739237</v>
+        <v>-35.06832138890954</v>
       </c>
       <c r="F15">
-        <v>-4.486927565944685</v>
+        <v>-1.945252005771976</v>
       </c>
       <c r="G15">
-        <v>-19.55979667671047</v>
+        <v>-15.92075563521402</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.08581058821403</v>
       </c>
       <c r="E16">
-        <v>-40.39632238924114</v>
+        <v>-36.01770464343261</v>
       </c>
       <c r="F16">
-        <v>-4.63457908528928</v>
+        <v>-2.059039865690127</v>
       </c>
       <c r="G16">
-        <v>-18.75636369033028</v>
+        <v>-14.9332430746682</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.35328503270911</v>
       </c>
       <c r="E17">
-        <v>-41.50892769665968</v>
+        <v>-35.9848098082409</v>
       </c>
       <c r="F17">
-        <v>-4.390520510872072</v>
+        <v>-1.65068704243868</v>
       </c>
       <c r="G17">
-        <v>-18.26318178970843</v>
+        <v>-15.177779831472</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.66556482210109</v>
       </c>
       <c r="E18">
-        <v>-41.46803331213341</v>
+        <v>-37.29823029552957</v>
       </c>
       <c r="F18">
-        <v>-4.143908079752035</v>
+        <v>-1.453492525467452</v>
       </c>
       <c r="G18">
-        <v>-18.15238776214565</v>
+        <v>-14.43881971946912</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.99061405291833</v>
       </c>
       <c r="E19">
-        <v>-41.15928648276445</v>
+        <v>-37.26753629870559</v>
       </c>
       <c r="F19">
-        <v>-3.948066286749578</v>
+        <v>-1.41967691135037</v>
       </c>
       <c r="G19">
-        <v>-18.35068447412968</v>
+        <v>-14.72798925123338</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.28231292507515</v>
       </c>
       <c r="E20">
-        <v>-42.24026266347641</v>
+        <v>-38.23490438775012</v>
       </c>
       <c r="F20">
-        <v>-4.173252166628805</v>
+        <v>-1.464769090921761</v>
       </c>
       <c r="G20">
-        <v>-18.21641702342069</v>
+        <v>-14.32633896895408</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.512552773425</v>
       </c>
       <c r="E21">
-        <v>-43.25528162026666</v>
+        <v>-37.90783308830913</v>
       </c>
       <c r="F21">
-        <v>-3.859657947318398</v>
+        <v>-1.267635873138341</v>
       </c>
       <c r="G21">
-        <v>-18.03807793522015</v>
+        <v>-14.41770174947411</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.66999975587695</v>
       </c>
       <c r="E22">
-        <v>-43.94098541874511</v>
+        <v>-39.59314544652972</v>
       </c>
       <c r="F22">
-        <v>-4.007813114043896</v>
+        <v>-1.096876216725251</v>
       </c>
       <c r="G22">
-        <v>-18.21820968383021</v>
+        <v>-13.98297415143918</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.738025724307</v>
       </c>
       <c r="E23">
-        <v>-43.30611600523977</v>
+        <v>-39.21773947976785</v>
       </c>
       <c r="F23">
-        <v>-4.003170114751204</v>
+        <v>-1.191425243713383</v>
       </c>
       <c r="G23">
-        <v>-17.85750753932614</v>
+        <v>-14.3959514652811</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.6937842450128</v>
       </c>
       <c r="E24">
-        <v>-43.87781773481212</v>
+        <v>-39.23706927106959</v>
       </c>
       <c r="F24">
-        <v>-3.899904177583412</v>
+        <v>-1.174317800110768</v>
       </c>
       <c r="G24">
-        <v>-17.90198471864625</v>
+        <v>-13.84839219890396</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.54384333287045</v>
       </c>
       <c r="E25">
-        <v>-44.0807816755989</v>
+        <v>-39.80251491380034</v>
       </c>
       <c r="F25">
-        <v>-4.14004540255278</v>
+        <v>-1.189274801935716</v>
       </c>
       <c r="G25">
-        <v>-18.24159206697408</v>
+        <v>-13.86848058923625</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.30614510246038</v>
       </c>
       <c r="E26">
-        <v>-43.90701280673957</v>
+        <v>-40.08781330475759</v>
       </c>
       <c r="F26">
-        <v>-3.865077955234915</v>
+        <v>-1.427144643486608</v>
       </c>
       <c r="G26">
-        <v>-17.71075602138856</v>
+        <v>-14.16646444849882</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.99518505239336</v>
       </c>
       <c r="E27">
-        <v>-44.30401959451802</v>
+        <v>-39.74700940788833</v>
       </c>
       <c r="F27">
-        <v>-3.524245358985656</v>
+        <v>-1.125482228246126</v>
       </c>
       <c r="G27">
-        <v>-18.15390068145709</v>
+        <v>-14.18949260326999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.61572184546347</v>
       </c>
       <c r="E28">
-        <v>-44.46340602992899</v>
+        <v>-39.71741583024821</v>
       </c>
       <c r="F28">
-        <v>-3.689095442347174</v>
+        <v>-1.099976795913929</v>
       </c>
       <c r="G28">
-        <v>-17.78024933807617</v>
+        <v>-14.15711877844146</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.20151332012935</v>
       </c>
       <c r="E29">
-        <v>-43.77772940229459</v>
+        <v>-39.8002484125595</v>
       </c>
       <c r="F29">
-        <v>-3.667235654954698</v>
+        <v>-1.432147982599517</v>
       </c>
       <c r="G29">
-        <v>-19.0646913491303</v>
+        <v>-14.55911501272962</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.78523911656758</v>
       </c>
       <c r="E30">
-        <v>-44.33443056171653</v>
+        <v>-39.23723456037087</v>
       </c>
       <c r="F30">
-        <v>-4.178501530860345</v>
+        <v>-1.23475548581902</v>
       </c>
       <c r="G30">
-        <v>-17.68903056628709</v>
+        <v>-14.18954226145308</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.38822946420607</v>
       </c>
       <c r="E31">
-        <v>-43.85346813007288</v>
+        <v>-38.84853978663349</v>
       </c>
       <c r="F31">
-        <v>-3.908529138981361</v>
+        <v>-0.8441877107056783</v>
       </c>
       <c r="G31">
-        <v>-18.45433599969149</v>
+        <v>-14.20646577024984</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.01444148824853</v>
       </c>
       <c r="E32">
-        <v>-42.95627553848821</v>
+        <v>-39.08367627100777</v>
       </c>
       <c r="F32">
-        <v>-3.756701819559253</v>
+        <v>-1.007300707623526</v>
       </c>
       <c r="G32">
-        <v>-18.06718921741973</v>
+        <v>-14.64021013625961</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.68970681072927</v>
       </c>
       <c r="E33">
-        <v>-43.32847308141564</v>
+        <v>-38.73708498435671</v>
       </c>
       <c r="F33">
-        <v>-3.922518607679839</v>
+        <v>-1.151777923080594</v>
       </c>
       <c r="G33">
-        <v>-18.13711952611853</v>
+        <v>-14.49149546481724</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.42658458798432</v>
       </c>
       <c r="E34">
-        <v>-42.58260397727128</v>
+        <v>-38.60149794409305</v>
       </c>
       <c r="F34">
-        <v>-3.961178514368492</v>
+        <v>-1.102448644243883</v>
       </c>
       <c r="G34">
-        <v>-17.9016602851834</v>
+        <v>-15.08789355426248</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.2213404364735</v>
       </c>
       <c r="E35">
-        <v>-42.92270369643234</v>
+        <v>-38.24025704402718</v>
       </c>
       <c r="F35">
-        <v>-3.894571976611592</v>
+        <v>-0.989436136214752</v>
       </c>
       <c r="G35">
-        <v>-18.08071114067489</v>
+        <v>-14.98672162730958</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.05433314324243</v>
       </c>
       <c r="E36">
-        <v>-42.51468592410423</v>
+        <v>-37.50001456883736</v>
       </c>
       <c r="F36">
-        <v>-3.801740155249462</v>
+        <v>-1.097426252680709</v>
       </c>
       <c r="G36">
-        <v>-18.55573304374106</v>
+        <v>-14.96340711034927</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.93080173109332</v>
       </c>
       <c r="E37">
-        <v>-41.92624695459953</v>
+        <v>-37.2573879884544</v>
       </c>
       <c r="F37">
-        <v>-3.856842326516283</v>
+        <v>-1.175035994648995</v>
       </c>
       <c r="G37">
-        <v>-17.84683434050753</v>
+        <v>-15.00355409610401</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.84407576066102</v>
       </c>
       <c r="E38">
-        <v>-40.46676280243045</v>
+        <v>-36.90127558520221</v>
       </c>
       <c r="F38">
-        <v>-3.507132945178624</v>
+        <v>-0.8984242380365731</v>
       </c>
       <c r="G38">
-        <v>-18.43736614325719</v>
+        <v>-15.67461822964197</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.77842284924715</v>
       </c>
       <c r="E39">
-        <v>-40.40345473580322</v>
+        <v>-36.66242801637865</v>
       </c>
       <c r="F39">
-        <v>-3.729181797703448</v>
+        <v>-0.8713921245810169</v>
       </c>
       <c r="G39">
-        <v>-18.29219375554184</v>
+        <v>-14.87898488855231</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.71179952881793</v>
       </c>
       <c r="E40">
-        <v>-40.38524574181838</v>
+        <v>-35.82681361435028</v>
       </c>
       <c r="F40">
-        <v>-3.987232325921342</v>
+        <v>-0.8149604236327034</v>
       </c>
       <c r="G40">
-        <v>-17.98858362413528</v>
+        <v>-15.11650825463117</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.65092650236135</v>
       </c>
       <c r="E41">
-        <v>-40.83253896921501</v>
+        <v>-36.01302220130868</v>
       </c>
       <c r="F41">
-        <v>-4.009840129078546</v>
+        <v>-0.7916062614455769</v>
       </c>
       <c r="G41">
-        <v>-19.07809905856435</v>
+        <v>-15.32140619442051</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.59194291630988</v>
       </c>
       <c r="E42">
-        <v>-40.32517100563263</v>
+        <v>-35.70677735382896</v>
       </c>
       <c r="F42">
-        <v>-3.405604094454502</v>
+        <v>-1.04698778989165</v>
       </c>
       <c r="G42">
-        <v>-18.06748220069996</v>
+        <v>-15.65488903350069</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.52545793617585</v>
       </c>
       <c r="E43">
-        <v>-40.26544722618247</v>
+        <v>-35.88171004050826</v>
       </c>
       <c r="F43">
-        <v>-3.636627479421257</v>
+        <v>-0.8080394139823135</v>
       </c>
       <c r="G43">
-        <v>-19.01745648537598</v>
+        <v>-14.85358803844779</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.44022943059659</v>
       </c>
       <c r="E44">
-        <v>-39.06312605596096</v>
+        <v>-34.08184766802665</v>
       </c>
       <c r="F44">
-        <v>-3.833019308379172</v>
+        <v>-0.9270501303751156</v>
       </c>
       <c r="G44">
-        <v>-18.99623257792371</v>
+        <v>-15.33388695110357</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.35224243678512</v>
       </c>
       <c r="E45">
-        <v>-38.56283609725257</v>
+        <v>-34.13314169311153</v>
       </c>
       <c r="F45">
-        <v>-3.699643044487021</v>
+        <v>-0.5619844741243596</v>
       </c>
       <c r="G45">
-        <v>-19.37903923499349</v>
+        <v>-15.64896315698539</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.26521249006575</v>
       </c>
       <c r="E46">
-        <v>-38.83005002726018</v>
+        <v>-34.21923704094535</v>
       </c>
       <c r="F46">
-        <v>-3.742492005131631</v>
+        <v>-0.7847250134305214</v>
       </c>
       <c r="G46">
-        <v>-18.78414744376861</v>
+        <v>-15.95629103103255</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.17542605075926</v>
       </c>
       <c r="E47">
-        <v>-38.33081746723258</v>
+        <v>-32.54459150324983</v>
       </c>
       <c r="F47">
-        <v>-3.587720667959974</v>
+        <v>-0.5934069348147532</v>
       </c>
       <c r="G47">
-        <v>-19.50954590596987</v>
+        <v>-15.49634535235222</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.07929287598448</v>
       </c>
       <c r="E48">
-        <v>-38.25613160966108</v>
+        <v>-32.7393407921867</v>
       </c>
       <c r="F48">
-        <v>-3.422921115010026</v>
+        <v>-0.9423202550783217</v>
       </c>
       <c r="G48">
-        <v>-18.82422490806703</v>
+        <v>-15.85367405095177</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.99413206809507</v>
       </c>
       <c r="E49">
-        <v>-37.68675525149166</v>
+        <v>-32.73239637729593</v>
       </c>
       <c r="F49">
-        <v>-3.457981765333515</v>
+        <v>-0.7099930198195612</v>
       </c>
       <c r="G49">
-        <v>-19.92435064094947</v>
+        <v>-16.14861717413651</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.92224803850165</v>
       </c>
       <c r="E50">
-        <v>-36.87922870949586</v>
+        <v>-31.75580152246077</v>
       </c>
       <c r="F50">
-        <v>-3.402805041000443</v>
+        <v>-0.5592790261868164</v>
       </c>
       <c r="G50">
-        <v>-19.28525313513871</v>
+        <v>-15.84060567243549</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.85580842309759</v>
       </c>
       <c r="E51">
-        <v>-36.48550732960998</v>
+        <v>-31.22954076531839</v>
       </c>
       <c r="F51">
-        <v>-3.482971124773768</v>
+        <v>-0.3233674451761424</v>
       </c>
       <c r="G51">
-        <v>-19.06512503059595</v>
+        <v>-16.6986874893052</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.79300723609997</v>
       </c>
       <c r="E52">
-        <v>-36.36624317390697</v>
+        <v>-31.5719703843564</v>
       </c>
       <c r="F52">
-        <v>-3.024463140385019</v>
+        <v>-0.4209449833889101</v>
       </c>
       <c r="G52">
-        <v>-19.52451619289845</v>
+        <v>-16.77121161043401</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.74539647860042</v>
       </c>
       <c r="E53">
-        <v>-35.8846829836943</v>
+        <v>-30.70640239100429</v>
       </c>
       <c r="F53">
-        <v>-3.353279439089269</v>
+        <v>-0.7036129340831995</v>
       </c>
       <c r="G53">
-        <v>-19.34861035566928</v>
+        <v>-16.11976245921623</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.71167541581582</v>
       </c>
       <c r="E54">
-        <v>-35.95396637177465</v>
+        <v>-30.81176639574076</v>
       </c>
       <c r="F54">
-        <v>-3.497547077593428</v>
+        <v>-0.6381329759941069</v>
       </c>
       <c r="G54">
-        <v>-19.76148504259949</v>
+        <v>-16.21199756848586</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.67859243811804</v>
       </c>
       <c r="E55">
-        <v>-35.55209600291196</v>
+        <v>-30.19624262319618</v>
       </c>
       <c r="F55">
-        <v>-3.333131887118379</v>
+        <v>-0.7451224246374827</v>
       </c>
       <c r="G55">
-        <v>-19.1730752995405</v>
+        <v>-16.67922810262536</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.64552024614546</v>
       </c>
       <c r="E56">
-        <v>-35.43336620714185</v>
+        <v>-29.67207175680834</v>
       </c>
       <c r="F56">
-        <v>-3.451584283881695</v>
+        <v>-0.6079911713084413</v>
       </c>
       <c r="G56">
-        <v>-19.60495086259336</v>
+        <v>-16.53022541372107</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.61886717653166</v>
       </c>
       <c r="E57">
-        <v>-35.60003442875716</v>
+        <v>-30.05644410210539</v>
       </c>
       <c r="F57">
-        <v>-3.508771455901361</v>
+        <v>-0.6816305483151089</v>
       </c>
       <c r="G57">
-        <v>-19.03862080300854</v>
+        <v>-16.42152861675741</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.59542636994375</v>
       </c>
       <c r="E58">
-        <v>-34.62917488625271</v>
+        <v>-29.75461225254615</v>
       </c>
       <c r="F58">
-        <v>-3.522828850726869</v>
+        <v>-0.6412989962076067</v>
       </c>
       <c r="G58">
-        <v>-19.59232609717935</v>
+        <v>-16.01566401000661</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.55958272472849</v>
       </c>
       <c r="E59">
-        <v>-34.83518422580965</v>
+        <v>-29.29963646899551</v>
       </c>
       <c r="F59">
-        <v>-3.34710727357101</v>
+        <v>-0.6186737973349438</v>
       </c>
       <c r="G59">
-        <v>-19.08916455702937</v>
+        <v>-16.9188950469409</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.51544868906328</v>
       </c>
       <c r="E60">
-        <v>-34.89642730828938</v>
+        <v>-28.28183023645354</v>
       </c>
       <c r="F60">
-        <v>-3.26606394871812</v>
+        <v>-0.8364134826304049</v>
       </c>
       <c r="G60">
-        <v>-19.66492636085556</v>
+        <v>-16.72815134460471</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.46869476162517</v>
       </c>
       <c r="E61">
-        <v>-34.85024140188516</v>
+        <v>-29.0902805871469</v>
       </c>
       <c r="F61">
-        <v>-3.474795138508137</v>
+        <v>-0.6857665867572869</v>
       </c>
       <c r="G61">
-        <v>-20.22555731629452</v>
+        <v>-16.95595991479858</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.41778015284556</v>
       </c>
       <c r="E62">
-        <v>-32.92193792112398</v>
+        <v>-28.67988310172776</v>
       </c>
       <c r="F62">
-        <v>-3.296609996696352</v>
+        <v>-0.7103566731093902</v>
       </c>
       <c r="G62">
-        <v>-20.46866557269813</v>
+        <v>-17.49729866610743</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.35017422410505</v>
       </c>
       <c r="E63">
-        <v>-35.05048599403033</v>
+        <v>-28.73259906765105</v>
       </c>
       <c r="F63">
-        <v>-3.81175843061892</v>
+        <v>-0.7375296090234224</v>
       </c>
       <c r="G63">
-        <v>-20.3107575162932</v>
+        <v>-17.06621432343847</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.27559458274847</v>
       </c>
       <c r="E64">
-        <v>-33.63139809424667</v>
+        <v>-28.35281406652377</v>
       </c>
       <c r="F64">
-        <v>-3.617475625068532</v>
+        <v>-0.7512059548436422</v>
       </c>
       <c r="G64">
-        <v>-20.52911447897245</v>
+        <v>-16.89862788714948</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.2005713838721</v>
       </c>
       <c r="E65">
-        <v>-33.92501076348199</v>
+        <v>-27.65781104667057</v>
       </c>
       <c r="F65">
-        <v>-3.595295259491172</v>
+        <v>-0.8142057809287531</v>
       </c>
       <c r="G65">
-        <v>-20.46940547962616</v>
+        <v>-17.33460687139826</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.12434429470507</v>
       </c>
       <c r="E66">
-        <v>-34.34101902819663</v>
+        <v>-27.64569285022604</v>
       </c>
       <c r="F66">
-        <v>-3.40038952165388</v>
+        <v>-0.6378604431185859</v>
       </c>
       <c r="G66">
-        <v>-20.54907706857426</v>
+        <v>-17.10108926542192</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.03635449750292</v>
       </c>
       <c r="E67">
-        <v>-33.70780703617809</v>
+        <v>-29.10856203671586</v>
       </c>
       <c r="F67">
-        <v>-3.776317559657546</v>
+        <v>-0.7040304312542104</v>
       </c>
       <c r="G67">
-        <v>-20.45152191262301</v>
+        <v>-16.68903724905822</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.94718162322296</v>
       </c>
       <c r="E68">
-        <v>-33.11928881837826</v>
+        <v>-27.96385890553096</v>
       </c>
       <c r="F68">
-        <v>-3.701948390969012</v>
+        <v>-0.8147036297378355</v>
       </c>
       <c r="G68">
-        <v>-20.27508142228925</v>
+        <v>-17.31549840254559</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.86081392391801</v>
       </c>
       <c r="E69">
-        <v>-33.95981435046794</v>
+        <v>-28.53433341864723</v>
       </c>
       <c r="F69">
-        <v>-3.636768301879732</v>
+        <v>-0.9673104428859772</v>
       </c>
       <c r="G69">
-        <v>-20.16309228778678</v>
+        <v>-17.29092091246204</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.7739187239185</v>
       </c>
       <c r="E70">
-        <v>-33.25645629607059</v>
+        <v>-27.929053054308</v>
       </c>
       <c r="F70">
-        <v>-3.99415582067394</v>
+        <v>-0.9894560170324193</v>
       </c>
       <c r="G70">
-        <v>-19.82482239985682</v>
+        <v>-16.71897782291539</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.67573370896108</v>
       </c>
       <c r="E71">
-        <v>-33.24998284247663</v>
+        <v>-28.28892635522356</v>
       </c>
       <c r="F71">
-        <v>-3.941524669369671</v>
+        <v>-0.8329210856602023</v>
       </c>
       <c r="G71">
-        <v>-20.21054730281946</v>
+        <v>-17.38077242894339</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.57610890054662</v>
       </c>
       <c r="E72">
-        <v>-33.28377884399587</v>
+        <v>-27.93726317768391</v>
       </c>
       <c r="F72">
-        <v>-3.722836503398004</v>
+        <v>-0.9526110633233</v>
       </c>
       <c r="G72">
-        <v>-19.67821158010466</v>
+        <v>-17.05569009916912</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.47631906185626</v>
       </c>
       <c r="E73">
-        <v>-34.45794649131168</v>
+        <v>-28.12737304499992</v>
       </c>
       <c r="F73">
-        <v>-3.95235722989608</v>
+        <v>-1.062415304401388</v>
       </c>
       <c r="G73">
-        <v>-19.49113430695321</v>
+        <v>-16.81918141529805</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.3706104674356</v>
       </c>
       <c r="E74">
-        <v>-34.49799178696151</v>
+        <v>-28.47886414052727</v>
       </c>
       <c r="F74">
-        <v>-4.157634127616422</v>
+        <v>-1.086352637240086</v>
       </c>
       <c r="G74">
-        <v>-20.06749531952202</v>
+        <v>-16.81522696865139</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.24822323497409</v>
       </c>
       <c r="E75">
-        <v>-34.48144247870048</v>
+        <v>-28.75398252191527</v>
       </c>
       <c r="F75">
-        <v>-3.710960199944068</v>
+        <v>-1.200998685787537</v>
       </c>
       <c r="G75">
-        <v>-19.35695127515547</v>
+        <v>-17.03596752411891</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.11929557050431</v>
       </c>
       <c r="E76">
-        <v>-33.71704059467973</v>
+        <v>-28.41300201455972</v>
       </c>
       <c r="F76">
-        <v>-3.909376558834424</v>
+        <v>-1.180895037288996</v>
       </c>
       <c r="G76">
-        <v>-19.63145012436245</v>
+        <v>-16.74239993260573</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.98418167872338</v>
       </c>
       <c r="E77">
-        <v>-34.38286665650151</v>
+        <v>-28.16812931106895</v>
       </c>
       <c r="F77">
-        <v>-3.728676493587741</v>
+        <v>-1.271725523005962</v>
       </c>
       <c r="G77">
-        <v>-18.78497342488066</v>
+        <v>-16.704466046544</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.83806518850181</v>
       </c>
       <c r="E78">
-        <v>-33.98299787315021</v>
+        <v>-29.3918497852137</v>
       </c>
       <c r="F78">
-        <v>-3.847942347140605</v>
+        <v>-1.351802143099785</v>
       </c>
       <c r="G78">
-        <v>-19.35351161834017</v>
+        <v>-17.26298983974721</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.67382925214571</v>
       </c>
       <c r="E79">
-        <v>-34.96089013578857</v>
+        <v>-29.46849873626752</v>
       </c>
       <c r="F79">
-        <v>-4.114361042861579</v>
+        <v>-1.419084628657369</v>
       </c>
       <c r="G79">
-        <v>-19.45416213437063</v>
+        <v>-16.28972917774795</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.50468568424967</v>
       </c>
       <c r="E80">
-        <v>-34.93745301856188</v>
+        <v>-30.22073487486667</v>
       </c>
       <c r="F80">
-        <v>-4.317407147166183</v>
+        <v>-1.349766016023703</v>
       </c>
       <c r="G80">
-        <v>-19.00750167493939</v>
+        <v>-16.86623916486602</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.33269610653608</v>
       </c>
       <c r="E81">
-        <v>-35.29326654252955</v>
+        <v>-30.17420027596385</v>
       </c>
       <c r="F81">
-        <v>-3.852152110281632</v>
+        <v>-1.468638395060238</v>
       </c>
       <c r="G81">
-        <v>-19.15968414283415</v>
+        <v>-16.46050697993679</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.1541176478072</v>
       </c>
       <c r="E82">
-        <v>-36.9425979105222</v>
+        <v>-30.36359690862365</v>
       </c>
       <c r="F82">
-        <v>-4.015387705575094</v>
+        <v>-1.582046862707907</v>
       </c>
       <c r="G82">
-        <v>-19.29460873683269</v>
+        <v>-16.08449687285914</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.96713765557223</v>
       </c>
       <c r="E83">
-        <v>-36.73762559151302</v>
+        <v>-30.71748809537507</v>
       </c>
       <c r="F83">
-        <v>-4.457366446808382</v>
+        <v>-1.808710550033727</v>
       </c>
       <c r="G83">
-        <v>-18.45677918229947</v>
+        <v>-16.63188730141378</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.785961362036598</v>
       </c>
       <c r="E84">
-        <v>-36.95996007986761</v>
+        <v>-31.8916625354019</v>
       </c>
       <c r="F84">
-        <v>-4.379536359110952</v>
+        <v>-1.704627842606775</v>
       </c>
       <c r="G84">
-        <v>-19.29878830057602</v>
+        <v>-15.73724050906283</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.614566360731226</v>
       </c>
       <c r="E85">
-        <v>-38.47549768330364</v>
+        <v>-32.22016030415531</v>
       </c>
       <c r="F85">
-        <v>-4.393206077991948</v>
+        <v>-1.679896933796196</v>
       </c>
       <c r="G85">
-        <v>-18.22218068320456</v>
+        <v>-16.03640954362846</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.450486254328519</v>
       </c>
       <c r="E86">
-        <v>-39.3134148143649</v>
+        <v>-32.93630224067631</v>
       </c>
       <c r="F86">
-        <v>-4.25701667839989</v>
+        <v>-1.546952249320903</v>
       </c>
       <c r="G86">
-        <v>-18.67419263950003</v>
+        <v>-15.94254895649904</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.298918481828188</v>
       </c>
       <c r="E87">
-        <v>-39.3762292773253</v>
+        <v>-34.1294668364543</v>
       </c>
       <c r="F87">
-        <v>-4.693661561926552</v>
+        <v>-1.896997947824099</v>
       </c>
       <c r="G87">
-        <v>-18.70830781128222</v>
+        <v>-15.81389453575188</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.175692372945145</v>
       </c>
       <c r="E88">
-        <v>-39.23080186304298</v>
+        <v>-34.52107794745262</v>
       </c>
       <c r="F88">
-        <v>-4.687597084170656</v>
+        <v>-1.907781634673743</v>
       </c>
       <c r="G88">
-        <v>-18.29643456437764</v>
+        <v>-16.02723933248468</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.087995951886072</v>
       </c>
       <c r="E89">
-        <v>-41.33031336061214</v>
+        <v>-35.98682497917431</v>
       </c>
       <c r="F89">
-        <v>-4.555494020976608</v>
+        <v>-1.678370252672837</v>
       </c>
       <c r="G89">
-        <v>-18.57778789812368</v>
+        <v>-15.18554306076159</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.032929625152279</v>
       </c>
       <c r="E90">
-        <v>-41.30209870330735</v>
+        <v>-36.96417608916875</v>
       </c>
       <c r="F90">
-        <v>-5.180118662485755</v>
+        <v>-1.916865511612842</v>
       </c>
       <c r="G90">
-        <v>-17.64355360221413</v>
+        <v>-15.95580769138382</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.020288497773038</v>
       </c>
       <c r="E91">
-        <v>-42.35670331563565</v>
+        <v>-37.62018668357891</v>
       </c>
       <c r="F91">
-        <v>-4.526217860226868</v>
+        <v>-2.474491797583566</v>
       </c>
       <c r="G91">
-        <v>-17.85016805986558</v>
+        <v>-15.53784138541422</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.063271791799988</v>
       </c>
       <c r="E92">
-        <v>-43.46001845862745</v>
+        <v>-38.46658111798254</v>
       </c>
       <c r="F92">
-        <v>-4.421976934625981</v>
+        <v>-2.206822267084364</v>
       </c>
       <c r="G92">
-        <v>-18.00785927553768</v>
+        <v>-15.58419564405509</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.166963851690591</v>
       </c>
       <c r="E93">
-        <v>-44.03906763727724</v>
+        <v>-40.57266343133683</v>
       </c>
       <c r="F93">
-        <v>-4.800422381166754</v>
+        <v>-2.406012321128936</v>
       </c>
       <c r="G93">
-        <v>-18.43218845003377</v>
+        <v>-15.48884034561469</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.321874451560832</v>
       </c>
       <c r="E94">
-        <v>-46.32615079248112</v>
+        <v>-41.37135492054366</v>
       </c>
       <c r="F94">
-        <v>-5.202408372560285</v>
+        <v>-2.421043047652733</v>
       </c>
       <c r="G94">
-        <v>-18.66393325887383</v>
+        <v>-15.97071507794716</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.535779447269849</v>
       </c>
       <c r="E95">
-        <v>-46.59890304620011</v>
+        <v>-43.08855226425226</v>
       </c>
       <c r="F95">
-        <v>-5.232143448851176</v>
+        <v>-2.668776259868759</v>
       </c>
       <c r="G95">
-        <v>-18.61852250571165</v>
+        <v>-15.91901428826036</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.817148585302602</v>
       </c>
       <c r="E96">
-        <v>-47.70174496365811</v>
+        <v>-44.69748964409649</v>
       </c>
       <c r="F96">
-        <v>-5.367212067347246</v>
+        <v>-2.54263827034227</v>
       </c>
       <c r="G96">
-        <v>-18.33884430800848</v>
+        <v>-15.92554764988211</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.15611651765335</v>
       </c>
       <c r="E97">
-        <v>-48.74984442307439</v>
+        <v>-45.85003835649968</v>
       </c>
       <c r="F97">
-        <v>-5.373980657395522</v>
+        <v>-2.96224197965854</v>
       </c>
       <c r="G97">
-        <v>-18.7420257175997</v>
+        <v>-15.93590800214726</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.54783637898571</v>
       </c>
       <c r="E98">
-        <v>-50.80000234667096</v>
+        <v>-47.78859656665122</v>
       </c>
       <c r="F98">
-        <v>-5.769768803881306</v>
+        <v>-3.237740410481599</v>
       </c>
       <c r="G98">
-        <v>-20.04902247541288</v>
+        <v>-16.01358664268072</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.97720036636307</v>
       </c>
       <c r="E99">
-        <v>-52.15653277439416</v>
+        <v>-48.86398574255622</v>
       </c>
       <c r="F99">
-        <v>-6.029643397120164</v>
+        <v>-3.157299308730545</v>
       </c>
       <c r="G99">
-        <v>-19.25466203908307</v>
+        <v>-16.03470957849404</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.46842981703832</v>
       </c>
       <c r="E100">
-        <v>-53.12628397288523</v>
+        <v>-51.00350744010166</v>
       </c>
       <c r="F100">
-        <v>-5.418130154862527</v>
+        <v>-3.445556254291523</v>
       </c>
       <c r="G100">
-        <v>-18.89328288801623</v>
+        <v>-16.37920991312891</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.96667449130882</v>
       </c>
       <c r="E101">
-        <v>-54.7957002552204</v>
+        <v>-51.91291332608501</v>
       </c>
       <c r="F101">
-        <v>-6.457467410358114</v>
+        <v>-3.676052797590096</v>
       </c>
       <c r="G101">
-        <v>-19.22432088921565</v>
+        <v>-16.15741825945267</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.52737021763475</v>
       </c>
       <c r="E102">
-        <v>-55.74394799488604</v>
+        <v>-54.48156567390081</v>
       </c>
       <c r="F102">
-        <v>-6.256525359256622</v>
+        <v>-3.831014659264397</v>
       </c>
       <c r="G102">
-        <v>-19.51569689958184</v>
+        <v>-16.55526638018012</v>
       </c>
     </row>
   </sheetData>
